--- a/resultat/resultats_mineraux.xlsx
+++ b/resultat/resultats_mineraux.xlsx
@@ -389,12 +389,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.9283 ± 0.13a</t>
+          <t>0.9283 ± 0.09a</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.0374 ± 0.04a</t>
+          <t>1.0374 ± 0.03a</t>
         </is>
       </c>
     </row>
@@ -411,12 +411,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0594 ± 0.01ab</t>
+          <t>0.0594 ± 0.01a</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.0417 ± 0.02a</t>
+          <t>0.0417 ± 0.01a</t>
         </is>
       </c>
     </row>
@@ -428,7 +428,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.0538 ± 0b</t>
+          <t>0.0538 ± 0c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -438,7 +438,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.0098 ± 0a</t>
+          <t>0.0098 ± 0b</t>
         </is>
       </c>
     </row>
@@ -450,7 +450,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.005 ± 0b</t>
+          <t>0.005 ± 0c</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -460,7 +460,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.0034 ± 0a</t>
+          <t>0.0034 ± 0b</t>
         </is>
       </c>
     </row>
@@ -499,12 +499,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.3288 ± 0.08a</t>
+          <t>0.3288 ± 0.06a</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.3038 ± 0.05a</t>
+          <t>0.3038 ± 0.03a</t>
         </is>
       </c>
     </row>
